--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484754_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484754_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6954</v>
+        <v>5.7484</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9211</v>
+        <v>2.318</v>
       </c>
       <c r="F2" t="n">
-        <v>3.7743</v>
+        <v>3.4304</v>
       </c>
       <c r="G2" t="n">
         <v>7.0028</v>
@@ -610,13 +610,13 @@
         <v>2.6418</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8929</v>
+        <v>0.9459</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7853</v>
+        <v>0.1822</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1076</v>
+        <v>0.7637</v>
       </c>
       <c r="V2" t="n">
         <v>-0.1245</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. GARCIA RUIZ</t>
+          <t>J. CALERO SEVILLANO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7466</v>
+        <v>4.7038</v>
       </c>
       <c r="E3" t="n">
-        <v>1.56</v>
+        <v>3.1073</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1866</v>
+        <v>1.5965</v>
       </c>
       <c r="G3" t="n">
-        <v>0.802</v>
+        <v>2.3498</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4625</v>
+        <v>1.2443</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2645</v>
+        <v>1.1055</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6941000000000001</v>
+        <v>2.2645</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.7865</v>
+        <v>1.5057</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4807</v>
+        <v>0.7588</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1078</v>
+        <v>0.0852</v>
       </c>
       <c r="N3" t="n">
-        <v>0.324</v>
+        <v>-0.2614</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2162</v>
+        <v>0.3466</v>
       </c>
       <c r="P3" t="n">
-        <v>2.2644</v>
+        <v>1.5096</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2644</v>
+        <v>2.4531</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8047</v>
+        <v>0.8444</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8658</v>
+        <v>0.5411</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9389</v>
+        <v>0.3034</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1245</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1245</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. CALERO SEVILLANO</t>
+          <t>A. GARCIA RUIZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.3461</v>
+        <v>4.4576</v>
       </c>
       <c r="E4" t="n">
-        <v>3.067</v>
+        <v>1.4827</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2791</v>
+        <v>2.9749</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3498</v>
+        <v>0.802</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2443</v>
+        <v>-0.4625</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1055</v>
+        <v>1.2645</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2645</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5057</v>
+        <v>-0.7865</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7588</v>
+        <v>1.4807</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0852</v>
+        <v>0.1078</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2614</v>
+        <v>0.324</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3466</v>
+        <v>-0.2162</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5096</v>
+        <v>2.2644</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.4531</v>
+        <v>2.2644</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4867</v>
+        <v>1.5158</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5008</v>
+        <v>0.7885</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0141</v>
+        <v>0.7272</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.1245</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2452</v>
+        <v>-0.1245</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. GONZALEZ LÓPEZ</t>
+          <t>J. GARCIA CORBI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8678</v>
+        <v>2.7586</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8678</v>
+        <v>0.9667</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1.7919</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8678</v>
+        <v>0.3729</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6339</v>
+        <v>-0.7677</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2339</v>
+        <v>1.1406</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8678</v>
+        <v>0.3248</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6339</v>
+        <v>-1.1403</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2339</v>
+        <v>1.4651</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.3725</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0.3245</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.2644</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.2644</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.7439</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.4039</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.6226</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.9244</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. GARCIA CORBI</t>
+          <t>J. GONZALEZ LÓPEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6743</v>
+        <v>1.8678</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1469</v>
+        <v>1.8678</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5274</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3729</v>
+        <v>1.8678</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7677</v>
+        <v>0.6339</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1406</v>
+        <v>1.2339</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3248</v>
+        <v>1.8678</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.1403</v>
+        <v>0.6339</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4651</v>
+        <v>1.2339</v>
       </c>
       <c r="M6" t="n">
-        <v>0.048</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3725</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3245</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2644</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2644</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3404</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4797</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1394</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6226</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.9244</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1268</v>
+        <v>1.4321</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5888</v>
+        <v>1.5501</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4619</v>
+        <v>-0.118</v>
       </c>
       <c r="G7" t="n">
         <v>1.4318</v>
@@ -1000,13 +1000,13 @@
         <v>1.3209</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2751</v>
+        <v>0.0301</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1147</v>
+        <v>-0.1533</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1605</v>
+        <v>0.1834</v>
       </c>
       <c r="V7" t="n">
         <v>-1.3507</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1046</v>
+        <v>1.1575</v>
       </c>
       <c r="E8" t="n">
         <v>1.2637</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1591</v>
+        <v>-0.1062</v>
       </c>
       <c r="G8" t="n">
         <v>2.398</v>
@@ -1078,13 +1078,13 @@
         <v>0.1887</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2369</v>
+        <v>-0.184</v>
       </c>
       <c r="T8" t="n">
         <v>-0.1764</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0605</v>
+        <v>-0.0076</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2452</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. PUJALTE MIRA</t>
+          <t>V. VICENT TORTOSA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7995</v>
+        <v>0.6818</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4864</v>
+        <v>-0.5686</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2858</v>
+        <v>1.2504</v>
       </c>
       <c r="G9" t="n">
-        <v>3.0966</v>
+        <v>3.1435</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5209</v>
+        <v>1.3469</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4243</v>
+        <v>1.7967</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9073</v>
+        <v>3.0955</v>
       </c>
       <c r="K9" t="n">
-        <v>2.7258</v>
+        <v>1.1042</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1816</v>
+        <v>1.9913</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1892</v>
+        <v>0.048</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7951</v>
+        <v>0.2426</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6059</v>
+        <v>-0.1946</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.887</v>
+        <v>-2.2644</v>
       </c>
       <c r="Q9" t="n">
         <v>-3.774</v>
       </c>
       <c r="R9" t="n">
-        <v>1.887</v>
+        <v>1.5096</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1369</v>
+        <v>0.229</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3803</v>
+        <v>-0.192</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7566000000000001</v>
+        <v>0.421</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.547</v>
+        <v>-0.4263</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.547</v>
+        <v>-0.7281</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V. VICENT TORTOSA</t>
+          <t>J. PUJALTE MIRA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4281</v>
+        <v>0.5698</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8223</v>
+        <v>-0.5838</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2504</v>
+        <v>1.1536</v>
       </c>
       <c r="G10" t="n">
-        <v>3.1435</v>
+        <v>3.0966</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3469</v>
+        <v>3.5209</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7967</v>
+        <v>-0.4243</v>
       </c>
       <c r="J10" t="n">
-        <v>3.0955</v>
+        <v>2.9073</v>
       </c>
       <c r="K10" t="n">
-        <v>1.1042</v>
+        <v>2.7258</v>
       </c>
       <c r="L10" t="n">
-        <v>1.9913</v>
+        <v>0.1816</v>
       </c>
       <c r="M10" t="n">
-        <v>0.048</v>
+        <v>0.1892</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2426</v>
+        <v>0.7951</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1946</v>
+        <v>-0.6059</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.2644</v>
+        <v>-1.887</v>
       </c>
       <c r="Q10" t="n">
         <v>-3.774</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5096</v>
+        <v>1.887</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0247</v>
+        <v>0.9072</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4456</v>
+        <v>0.2829</v>
       </c>
       <c r="U10" t="n">
-        <v>0.421</v>
+        <v>0.6243</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.4263</v>
+        <v>-1.547</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.7281</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2022</v>
+        <v>0.3344</v>
       </c>
       <c r="E11" t="n">
         <v>-0.113</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3151</v>
+        <v>0.4474</v>
       </c>
       <c r="G11" t="n">
         <v>0.5502</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.348</v>
+        <v>-0.2157</v>
       </c>
       <c r="T11" t="n">
         <v>-0.1764</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1716</v>
+        <v>-0.0394</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.025</v>
+        <v>0.1044</v>
       </c>
       <c r="E12" t="n">
         <v>-0.0764</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1014</v>
+        <v>0.1808</v>
       </c>
       <c r="G12" t="n">
         <v>0.0897</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.06469999999999999</v>
+        <v>0.0147</v>
       </c>
       <c r="T12" t="n">
         <v>-0.1176</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0529</v>
+        <v>0.1323</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.6821</v>
+        <v>-0.43</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.2407</v>
+        <v>-1.4596</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5587</v>
+        <v>1.0296</v>
       </c>
       <c r="G13" t="n">
         <v>-1.027</v>
@@ -1468,13 +1468,13 @@
         <v>2.0757</v>
       </c>
       <c r="S13" t="n">
-        <v>0.458</v>
+        <v>0.71</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.786</v>
+        <v>-0.0049</v>
       </c>
       <c r="U13" t="n">
-        <v>1.244</v>
+        <v>0.7149</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2452</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.0077</v>
+        <v>-5.5899</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.0136</v>
+        <v>-3.6222</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.9941</v>
+        <v>-1.9677</v>
       </c>
       <c r="G14" t="n">
         <v>-3.4833</v>
@@ -1546,13 +1546,13 @@
         <v>2.2644</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0041</v>
+        <v>0.4137</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.254</v>
+        <v>0.1373</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2499</v>
+        <v>0.2763</v>
       </c>
       <c r="V14" t="n">
         <v>-3.8411</v>
@@ -1579,19 +1579,19 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>16.3266</v>
+        <v>17.7963</v>
       </c>
       <c r="E15" t="n">
-        <v>4.6629</v>
+        <v>6.132700000000002</v>
       </c>
       <c r="F15" t="n">
-        <v>11.6637</v>
+        <v>11.6636</v>
       </c>
       <c r="G15" t="n">
         <v>18.5948</v>
       </c>
       <c r="H15" t="n">
-        <v>7.231299999999997</v>
+        <v>7.231299999999999</v>
       </c>
       <c r="I15" t="n">
         <v>11.3632</v>
@@ -1609,10 +1609,10 @@
         <v>0.6660999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.09380000000000011</v>
+        <v>-0.09379999999999988</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7599</v>
+        <v>0.7598999999999998</v>
       </c>
       <c r="P15" t="n">
         <v>3.774</v>
@@ -1624,13 +1624,13 @@
         <v>18.87</v>
       </c>
       <c r="S15" t="n">
-        <v>4.485300000000001</v>
+        <v>5.955</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.01820000000000022</v>
+        <v>1.4514</v>
       </c>
       <c r="U15" t="n">
-        <v>4.5036</v>
+        <v>4.503399999999999</v>
       </c>
       <c r="V15" t="n">
         <v>-10.5271</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.4083</v>
+        <v>4.1665</v>
       </c>
       <c r="E16" t="n">
-        <v>5.1346</v>
+        <v>4.4526</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7264</v>
+        <v>-0.2861</v>
       </c>
       <c r="G16" t="n">
         <v>-0.8702</v>
@@ -1702,13 +1702,13 @@
         <v>2.6418</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1364</v>
+        <v>-0.3781</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0283</v>
+        <v>-0.7104</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1081</v>
+        <v>0.3322</v>
       </c>
       <c r="V16" t="n">
         <v>4.66</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0198</v>
+        <v>1.2592</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2766</v>
+        <v>0.5689</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7432</v>
+        <v>0.6903</v>
       </c>
       <c r="G17" t="n">
         <v>0.6609</v>
@@ -1780,13 +1780,13 @@
         <v>0.9435</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2828</v>
+        <v>-0.0434</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7642</v>
+        <v>-0.4719</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4815</v>
+        <v>0.4286</v>
       </c>
       <c r="V17" t="n">
         <v>-0.3018</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. NÚÑEZ NIEVAS</t>
+          <t>B. TERREROS RIVAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9339</v>
+        <v>1.1739</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9339</v>
+        <v>1.33</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>-0.1561</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9339</v>
+        <v>-1.538</v>
       </c>
       <c r="H18" t="n">
-        <v>0.317</v>
+        <v>-0.0814</v>
       </c>
       <c r="I18" t="n">
-        <v>0.617</v>
+        <v>-1.4566</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9339</v>
+        <v>0.8721</v>
       </c>
       <c r="K18" t="n">
-        <v>0.317</v>
+        <v>0.8139</v>
       </c>
       <c r="L18" t="n">
-        <v>0.617</v>
+        <v>0.0582</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-2.41</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-0.8953</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-1.5148</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.1887</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.0757</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-0.2691</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-0.4473</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>0.1782</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>2.7922</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.7922</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. TERREROS RIVAS</t>
+          <t>J. NÚÑEZ NIEVAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2032</v>
+        <v>0.9339</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0377</v>
+        <v>0.9339</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8345</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.538</v>
+        <v>0.9339</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0814</v>
+        <v>0.317</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.4566</v>
+        <v>0.617</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8721</v>
+        <v>0.9339</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8139</v>
+        <v>0.317</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0582</v>
+        <v>0.617</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.41</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8953</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.5148</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1887</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0757</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2398</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7396</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5002</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>2.7922</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.7922</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.109</v>
+        <v>-0.1619</v>
       </c>
       <c r="E20" t="n">
         <v>-0.233</v>
       </c>
       <c r="F20" t="n">
-        <v>0.124</v>
+        <v>0.0711</v>
       </c>
       <c r="G20" t="n">
         <v>0.1295</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0823</v>
+        <v>0.0294</v>
       </c>
       <c r="T20" t="n">
         <v>-0.2352</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3175</v>
+        <v>0.2645</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3208</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. FERNANDEZ CARRASCO</t>
+          <t>B. ZHENG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9892</v>
+        <v>-1.122</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4938</v>
+        <v>0.024</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5046</v>
+        <v>-1.146</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.8838</v>
+        <v>-0.6448</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.9291</v>
+        <v>-0.7748</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.9547</v>
+        <v>0.1299</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.0398</v>
+        <v>0.4882</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4485</v>
+        <v>0.3803</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5914</v>
+        <v>0.1078</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.8439</v>
+        <v>-1.133</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.4806</v>
+        <v>-1.1551</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.3633</v>
+        <v>0.0221</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9435</v>
+        <v>0.3774</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R21" t="n">
-        <v>2.8305</v>
+        <v>1.3209</v>
       </c>
       <c r="S21" t="n">
-        <v>0.7248</v>
+        <v>-0.8546</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2068</v>
+        <v>-0.7659</v>
       </c>
       <c r="U21" t="n">
-        <v>0.518</v>
+        <v>-0.0887</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2262</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2262</v>
+        <v>1.2452</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2931</v>
+        <v>-1.2137</v>
       </c>
       <c r="E22" t="n">
         <v>-1.5131</v>
       </c>
       <c r="F22" t="n">
-        <v>0.22</v>
+        <v>0.2994</v>
       </c>
       <c r="G22" t="n">
         <v>-1.1696</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1235</v>
+        <v>-0.0441</v>
       </c>
       <c r="T22" t="n">
         <v>-0.2352</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1117</v>
+        <v>0.1911</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B. ZHENG</t>
+          <t>M. FERNANDEZ CARRASCO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.148</v>
+        <v>-1.4101</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.2683</v>
+        <v>-1.8835</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8797</v>
+        <v>0.4734</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.6448</v>
+        <v>-3.8838</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7748</v>
+        <v>-1.9291</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1299</v>
+        <v>-1.9547</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4882</v>
+        <v>-1.0398</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3803</v>
+        <v>-0.4485</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1078</v>
+        <v>-0.5914</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.133</v>
+        <v>-2.8439</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1551</v>
+        <v>-1.4806</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0221</v>
+        <v>-1.3633</v>
       </c>
       <c r="P23" t="n">
-        <v>0.3774</v>
+        <v>0.9435</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3209</v>
+        <v>2.8305</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.8805</v>
+        <v>0.3039</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0582</v>
+        <v>-0.1829</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8224</v>
+        <v>0.4868</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.2262</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2452</v>
+        <v>1.2262</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.3479</v>
+        <v>-2.3791</v>
       </c>
       <c r="E24" t="n">
         <v>-1.8424</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5054999999999999</v>
+        <v>-0.5367</v>
       </c>
       <c r="G24" t="n">
         <v>-1.3962</v>
@@ -2326,13 +2326,13 @@
         <v>0.1887</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1969</v>
+        <v>-0.2281</v>
       </c>
       <c r="T24" t="n">
         <v>-0.3527</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1558</v>
+        <v>0.1247</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.2761</v>
+        <v>-3.2436</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.2218</v>
+        <v>-2.3192</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.0543</v>
+        <v>-0.9244</v>
       </c>
       <c r="G25" t="n">
         <v>-2.9776</v>
@@ -2404,13 +2404,13 @@
         <v>1.5096</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2228</v>
+        <v>-0.1903</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1611</v>
+        <v>-0.2586</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0617</v>
+        <v>0.0682</v>
       </c>
       <c r="V25" t="n">
         <v>1.2452</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.7745</v>
+        <v>-4.9982</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.8824</v>
+        <v>-4.0772</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.8921</v>
+        <v>-0.9209000000000001</v>
       </c>
       <c r="G26" t="n">
         <v>-3.8892</v>
@@ -2482,13 +2482,13 @@
         <v>1.1322</v>
       </c>
       <c r="S26" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.5893</v>
       </c>
       <c r="T26" t="n">
-        <v>0.4391</v>
+        <v>0.2442</v>
       </c>
       <c r="U26" t="n">
-        <v>0.3739</v>
+        <v>0.3451</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-7.9538</v>
+        <v>-6.733</v>
       </c>
       <c r="E27" t="n">
-        <v>-7.5916</v>
+        <v>-7.1044</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.3622</v>
+        <v>0.3715</v>
       </c>
       <c r="G27" t="n">
         <v>-3.9493</v>
@@ -2560,13 +2560,13 @@
         <v>2.4531</v>
       </c>
       <c r="S27" t="n">
-        <v>-2.0228</v>
+        <v>-0.802</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.5749</v>
+        <v>-1.0878</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.4479</v>
+        <v>0.2858</v>
       </c>
       <c r="V27" t="n">
         <v>1.2262</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-16.3264</v>
+        <v>-13.7281</v>
       </c>
       <c r="E28" t="n">
-        <v>-11.6636</v>
+        <v>-11.6634</v>
       </c>
       <c r="F28" t="n">
-        <v>-4.6629</v>
+        <v>-2.0645</v>
       </c>
       <c r="G28" t="n">
         <v>-18.5944</v>
@@ -2638,13 +2638,13 @@
         <v>15.096</v>
       </c>
       <c r="S28" t="n">
-        <v>-4.4854</v>
+        <v>-1.8871</v>
       </c>
       <c r="T28" t="n">
-        <v>-4.503500000000001</v>
+        <v>-4.5037</v>
       </c>
       <c r="U28" t="n">
-        <v>0.01809999999999995</v>
+        <v>2.6165</v>
       </c>
       <c r="V28" t="n">
         <v>10.5272</v>
